--- a/Loan Workbook.xlsx
+++ b/Loan Workbook.xlsx
@@ -8,16 +8,43 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel Beginner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E01958C-05B5-4FB6-A2FC-7F1B4AAC2E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8DCE0E-A215-4F15-B792-E6F0AAFF4E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3855" yWindow="3855" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Terms of loan" sheetId="1" r:id="rId1"/>
     <sheet name="Detail sheet for 5-year loan" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Detail sheet for 5-year loan'!$4:$8</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Tamim</author>
+  </authors>
+  <commentList>
+    <comment ref="C9" authorId="0" shapeId="0" xr:uid="{6BB7D668-D0BC-4459-B7D0-CDC00D45CBAE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>This is the beginning balance of the loan.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -73,7 +100,7 @@
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -88,6 +115,13 @@
       <b/>
       <sz val="10"/>
       <name val="Helv"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1106,7 +1140,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B3:F70"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2454,10 +2488,13 @@
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="halfwidthKatakana" alignment="noControl"/>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
-    <oddHeader>&amp;A</oddHeader>
-    <oddFooter>Page &amp;P</oddFooter>
+    <oddHeader>&amp;R&amp;D&amp;T</oddHeader>
+    <oddFooter>&amp;CTamim</oddFooter>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Loan Workbook.xlsx
+++ b/Loan Workbook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel Beginner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8DCE0E-A215-4F15-B792-E6F0AAFF4E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234FC542-F41C-4D32-8249-C99889056958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,6 +40,30 @@
             <charset val="1"/>
           </rPr>
           <t>This is the beginning balance of the loan.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{ABE09BE6-FA10-4A7C-B873-E2705A2DE8B5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tamim:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
         </r>
       </text>
     </comment>
@@ -100,7 +124,7 @@
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -115,6 +139,12 @@
       <b/>
       <sz val="10"/>
       <name val="Helv"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>

--- a/Loan Workbook.xlsx
+++ b/Loan Workbook.xlsx
@@ -1,74 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel Beginner\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cindy\Desktop\Chris - Videos\Excel 2019\Module 4 - Navigating Workbooks\Module 4 - Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{234FC542-F41C-4D32-8249-C99889056958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97C3AD72-4762-42BD-96AD-CD49C6EBC59C}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20640" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Terms of loan" sheetId="1" r:id="rId1"/>
     <sheet name="Detail sheet for 5-year loan" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Detail sheet for 5-year loan'!$4:$8</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Tamim</author>
-  </authors>
-  <commentList>
-    <comment ref="C9" authorId="0" shapeId="0" xr:uid="{6BB7D668-D0BC-4459-B7D0-CDC00D45CBAE}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>This is the beginning balance of the loan.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{ABE09BE6-FA10-4A7C-B873-E2705A2DE8B5}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Tamim:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -124,7 +74,7 @@
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -139,19 +89,6 @@
       <b/>
       <sz val="10"/>
       <name val="Helv"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1170,7 +1107,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B3:F70"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2518,13 +2455,24 @@
     </row>
   </sheetData>
   <phoneticPr fontId="0" type="halfwidthKatakana" alignment="noControl"/>
-  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0">
-    <oddHeader>&amp;R&amp;D&amp;T</oddHeader>
-    <oddFooter>&amp;CTamim</oddFooter>
+    <oddHeader>&amp;A</oddHeader>
+    <oddFooter>Page &amp;P</oddFooter>
   </headerFooter>
-  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <phoneticPr fontId="0" type="halfwidthKatakana" alignment="noControl"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter alignWithMargins="0">
+    <oddHeader>&amp;A</oddHeader>
+    <oddFooter>Page &amp;P</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/Loan Workbook.xlsx
+++ b/Loan Workbook.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cindy\Desktop\Chris - Videos\Excel 2019\Module 4 - Navigating Workbooks\Module 4 - Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cindy\Desktop\Chris - Videos\Excel 2019\Module 5 - Page Setup &amp; Print Options\Module 5 - Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97C3AD72-4762-42BD-96AD-CD49C6EBC59C}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DED55967-5F5B-4182-A9F3-79F6A17D1A52}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20640" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Terms of loan" sheetId="1" r:id="rId1"/>

--- a/Loan Workbook.xlsx
+++ b/Loan Workbook.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cindy\Desktop\Chris - Videos\Excel 2019\Module 5 - Page Setup &amp; Print Options\Module 5 - Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cindy\Desktop\Chris - Videos\Excel 2019\Module 4 - Navigating Workbooks\Module 4 - Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DED55967-5F5B-4182-A9F3-79F6A17D1A52}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97C3AD72-4762-42BD-96AD-CD49C6EBC59C}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20640" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Terms of loan" sheetId="1" r:id="rId1"/>
